--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536299_LIGAREGULARB_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536299_LIGAREGULARB_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1455,7 +1455,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1467,67 +1467,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.6154</v>
+        <v>8.0161</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6708</v>
+        <v>3.5738</v>
       </c>
       <c r="F13" t="n">
-        <v>3.9445</v>
+        <v>4.4423</v>
       </c>
       <c r="G13" t="n">
-        <v>5.0172</v>
+        <v>6.1396</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0769</v>
+        <v>3.4969</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9402</v>
+        <v>2.6427</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4041</v>
+        <v>4.6471</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7723</v>
+        <v>3.4235</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6318</v>
+        <v>1.2236</v>
       </c>
       <c r="M13" t="n">
-        <v>1.613</v>
+        <v>1.4925</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3046</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3084</v>
+        <v>1.4191</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6439</v>
+        <v>0.411</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0274</v>
+        <v>-2.0548</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6713</v>
+        <v>2.4658</v>
       </c>
       <c r="S13" t="n">
-        <v>0.605</v>
+        <v>0.7669</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.9815</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1001</v>
+        <v>-0.2147</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3493</v>
+        <v>0.6986</v>
       </c>
       <c r="W13" t="n">
-        <v>0.589</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2397</v>
+        <v>0.6986</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. GARCIA RIERA</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1550,67 +1550,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.549</v>
+        <v>7.6154</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1067</v>
+        <v>3.6708</v>
       </c>
       <c r="F14" t="n">
-        <v>4.4423</v>
+        <v>3.9445</v>
       </c>
       <c r="G14" t="n">
-        <v>4.6725</v>
+        <v>5.0172</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6216</v>
+        <v>3.0769</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0509</v>
+        <v>1.9402</v>
       </c>
       <c r="J14" t="n">
-        <v>3.18</v>
+        <v>3.4041</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5482</v>
+        <v>2.7723</v>
       </c>
       <c r="L14" t="n">
         <v>0.6318</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4925</v>
+        <v>1.613</v>
       </c>
       <c r="N14" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.3046</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4191</v>
+        <v>1.3084</v>
       </c>
       <c r="P14" t="n">
-        <v>0.411</v>
+        <v>1.6439</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0548</v>
+        <v>-1.0274</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4658</v>
+        <v>2.6713</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7669</v>
+        <v>0.605</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9815</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2147</v>
+        <v>-0.1001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6986</v>
+        <v>0.3493</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.589</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6986</v>
+        <v>-0.2397</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. CARREÑO VIDAL</t>
+          <t>P. CARRENO VIDAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,64 +1716,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7671</v>
+        <v>2.1524</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7671</v>
+        <v>0.6691</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1.4833</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7671</v>
+        <v>4.5122</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5836</v>
+        <v>0.7896</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1836</v>
+        <v>3.7227</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7671</v>
+        <v>3.0992</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5836</v>
+        <v>0.5743</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1836</v>
+        <v>2.5249</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.413</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.2153</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.1977</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-2.2603</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.0822</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.8219</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.3392</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.4124</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.7516</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2397</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2397</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7671</v>
+        <v>1.3475</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7671</v>
+        <v>2.3093</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0.9618</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7671</v>
+        <v>-1.0536</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5836</v>
+        <v>-1.7326</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1836</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7671</v>
+        <v>1.319</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5836</v>
+        <v>-0.3391</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1836</v>
+        <v>1.6581</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-2.3726</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-1.3934</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.2055</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.2329</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.2573</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.8396</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.4177</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.9384</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1781</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2397</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,58 +1882,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4671</v>
+        <v>1.2129</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4671</v>
+        <v>0.547</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4671</v>
+        <v>-0.2074</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8753</v>
+        <v>1.4567</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5918</v>
+        <v>-1.6641</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4671</v>
+        <v>1.5494</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8753</v>
+        <v>2.8501</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5918</v>
+        <v>-1.3008</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.7567</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.3934</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.3633</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.4384</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.4658</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.0181</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.0251</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.0432</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3475</v>
+        <v>1.1002</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3093</v>
+        <v>-1.5399</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9618</v>
+        <v>2.64</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0536</v>
+        <v>1.1636</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7326</v>
+        <v>-0.3356</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6788999999999999</v>
+        <v>1.4992</v>
       </c>
       <c r="J19" t="n">
-        <v>1.319</v>
+        <v>0.3494</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3391</v>
+        <v>-0.1251</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6581</v>
+        <v>0.4746</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3726</v>
+        <v>0.8142</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3934</v>
+        <v>-0.2104</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9792</v>
+        <v>1.0246</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2055</v>
+        <v>-0.411</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0274</v>
+        <v>-2.0548</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2329</v>
+        <v>1.6439</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2573</v>
+        <v>-0.3511</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8396</v>
+        <v>0.1655</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4177</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9384</v>
+        <v>0.6986</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1781</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2397</v>
+        <v>0.6986</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2129</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.547</v>
+        <v>2.0459</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6657999999999999</v>
+        <v>-2.5837</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2074</v>
+        <v>0.6046</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4567</v>
+        <v>2.0331</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6641</v>
+        <v>-1.4285</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5494</v>
+        <v>2.5516</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8501</v>
+        <v>3.1428</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3008</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7567</v>
+        <v>-1.9469</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3934</v>
+        <v>-1.1096</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3633</v>
+        <v>-0.8373</v>
       </c>
       <c r="P20" t="n">
-        <v>1.4384</v>
+        <v>-1.0274</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0274</v>
+        <v>-2.0548</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4658</v>
+        <v>1.0274</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0181</v>
+        <v>1.3027</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0251</v>
+        <v>1.5492</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0432</v>
+        <v>-0.2465</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.4178</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.4178</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>K. KELIKI EBENGO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1002</v>
+        <v>-0.7119</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5399</v>
+        <v>-0.7936</v>
       </c>
       <c r="F21" t="n">
-        <v>2.64</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1636</v>
+        <v>0.3548</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3356</v>
+        <v>-0.1499</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4992</v>
+        <v>0.5046</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3494</v>
+        <v>0.1762</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1251</v>
+        <v>0.0973</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4746</v>
+        <v>0.0789</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8142</v>
+        <v>0.1786</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2104</v>
+        <v>-0.2471</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0246</v>
+        <v>0.4257</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.411</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0548</v>
+        <v>-1.0274</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6439</v>
+        <v>0.411</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3511</v>
+        <v>0.0292</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1655</v>
+        <v>0.0576</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.0284</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6986</v>
+        <v>-0.4794</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6986</v>
+        <v>-0.4794</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. CARRENO VIDAL</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3853</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.098</v>
+        <v>-1.9271</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4833</v>
+        <v>1.0042</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7451</v>
+        <v>-0.7953</v>
       </c>
       <c r="H22" t="n">
-        <v>0.206</v>
+        <v>-1.615</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5391</v>
+        <v>0.8197</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3321</v>
+        <v>-1.5043</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-1.5832</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3414</v>
+        <v>0.0789</v>
       </c>
       <c r="M22" t="n">
-        <v>1.413</v>
+        <v>0.709</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2153</v>
+        <v>-0.0318</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1977</v>
+        <v>0.7408</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.2603</v>
+        <v>0.8219</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.0822</v>
+        <v>-1.0274</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8219</v>
+        <v>1.8493</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3392</v>
+        <v>0.4683</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4124</v>
+        <v>0.6046</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7516</v>
+        <v>-0.1363</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2397</v>
+        <v>-1.4178</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2397</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.4178</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.9717</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0459</v>
+        <v>-0.3816</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5837</v>
+        <v>-0.59</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6046</v>
+        <v>-2.6715</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0331</v>
+        <v>-1.1888</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4285</v>
+        <v>-1.4827</v>
       </c>
       <c r="J23" t="n">
-        <v>2.5516</v>
+        <v>-1.2922</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1428</v>
+        <v>-0.5049</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.7873</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9469</v>
+        <v>-1.3793</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1096</v>
+        <v>-0.6839</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8373</v>
+        <v>-0.6954</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.0274</v>
+        <v>2.0548</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0548</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0274</v>
+        <v>2.0548</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3027</v>
+        <v>0.823</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5492</v>
+        <v>0.9106</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2465</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4178</v>
+        <v>-1.1781</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4178</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K. KELIKI EBENGO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,318 +2380,69 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7119</v>
+        <v>20.52360000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7936</v>
+        <v>11.7212</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08169999999999999</v>
+        <v>8.802200000000003</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3548</v>
+        <v>14.3806</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1499</v>
+        <v>6.887399999999998</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5046</v>
+        <v>7.493</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1762</v>
+        <v>16.6527</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0973</v>
+        <v>12.0688</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0789</v>
+        <v>4.5838</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1786</v>
+        <v>-2.271999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2471</v>
+        <v>-5.180999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4257</v>
+        <v>2.909</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6163999999999999</v>
+        <v>3.0823</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0274</v>
+        <v>-14.3836</v>
       </c>
       <c r="R24" t="n">
-        <v>0.411</v>
+        <v>17.466</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0292</v>
+        <v>4.279800000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0576</v>
+        <v>6.267399999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0284</v>
+        <v>-1.9877</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.4794</v>
+        <v>-1.2192</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.1849</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.4794</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>play_by_play_2536299_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>S. CAMPBELL</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>TQ-CB PRAT</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-0.9229000000000001</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-1.9271</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1.0042</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-0.7953</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-1.615</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.8197</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-1.5043</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-1.5832</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.0789</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-0.0318</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.7408</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0.8219</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-1.0274</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.8493</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.4683</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.6046</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-0.1363</v>
-      </c>
-      <c r="V25" t="n">
-        <v>-1.4178</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>-1.4178</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536299_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>S. COSTA I VAZQUEZ</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>TQ-CB PRAT</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-2.7388</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-2.1487</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-4.4386</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-1.7723</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-2.6663</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-3.0593</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-1.0884</v>
-      </c>
-      <c r="L26" t="n">
-        <v>-1.9709</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-1.3793</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-0.6839</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-0.6954</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.0548</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.0548</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.9106</v>
-      </c>
-      <c r="U26" t="n">
-        <v>-0.08749999999999999</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-1.1781</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>-1.1781</v>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>play_by_play_2536299_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>TQ-CB PRAT</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>20.5236</v>
-      </c>
-      <c r="E27" t="n">
-        <v>11.7212</v>
-      </c>
-      <c r="F27" t="n">
-        <v>8.802199999999999</v>
-      </c>
-      <c r="G27" t="n">
-        <v>14.3806</v>
-      </c>
-      <c r="H27" t="n">
-        <v>6.887500000000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>7.492999999999999</v>
-      </c>
-      <c r="J27" t="n">
-        <v>16.6527</v>
-      </c>
-      <c r="K27" t="n">
-        <v>12.0689</v>
-      </c>
-      <c r="L27" t="n">
-        <v>4.5839</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-2.271999999999999</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-5.180999999999999</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.909</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3.0823</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-14.3836</v>
-      </c>
-      <c r="R27" t="n">
-        <v>17.466</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.2798</v>
-      </c>
-      <c r="T27" t="n">
-        <v>6.267399999999999</v>
-      </c>
-      <c r="U27" t="n">
-        <v>-1.9877</v>
-      </c>
-      <c r="V27" t="n">
-        <v>-1.2192</v>
-      </c>
-      <c r="W27" t="n">
-        <v>3.1849</v>
-      </c>
-      <c r="X27" t="n">
         <v>-4.4041</v>
       </c>
-      <c r="Y27" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
